--- a/Accounting Pre-work/CMU METALS Prework Redesign/Learning_Objectives_Matrix.xlsx
+++ b/Accounting Pre-work/CMU METALS Prework Redesign/Learning_Objectives_Matrix.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002B4C7E"/>
-      <sz val="9"/>
+      <color rgb="0000356B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -44,46 +44,10 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A237E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001B5E20"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00E65100"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00B71C1C"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -92,42 +56,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B4C7E"/>
+        <fgColor rgb="0000356B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EDF3"/>
+        <fgColor rgb="00E8F0F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B5E20"/>
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004FC3F7"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FDECEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF8F00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00FFF9E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,46 +160,38 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -611,29 +557,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -741,49 +687,49 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>I. The System as an Evolved Information System</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="17" t="n"/>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Given two conventions applied to the same event, explain why they produce different representations and why neither is inherently wrong.</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Two conventions, neither wrong</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -817,27 +763,27 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="3" t="n">
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Given the same event under two sets of conventions, show the identity holds in both and explain what differs.</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Architecture vs. instances</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -866,83 +812,101 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>3*</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>DROPPED — IT vocabulary. Concept demonstrated through Objective 2.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>II. The Entity and Its Boundary</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="17" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Given a transaction between two entities in a group, show effects on each identity and explain why consolidated identity is unaffected.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Entity as boundary</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>Partial: Concept in rabbit hole; student hasn’t practiced it operationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Given a transaction between two entities in a group, show effects on each identity and explain why consolidated identity is unaffected.</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Entity as boundary</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Given resources that are and are not recorded, identify what determines entry and what this means for interpreting the balance sheet.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Recognition as gatekeeper</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="8" t="n"/>
@@ -954,108 +918,112 @@
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="Q7" s="12" t="inlineStr">
-        <is>
-          <t>Partial: Concept in rabbit hole; student hasn't practiced it operationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Entity boundary exercise + Module 4 §2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>III. Conventions, Worth, and Limits</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Given resources that are and are not recorded, identify what determines entry and what this means for interpreting the balance sheet.</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Recognition as gatekeeper</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="8" t="n"/>
-      <c r="Q8" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Entity boundary exercise + Module 4 §2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>III. Conventions, Worth, and Limits</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="17" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Given two conventions on the same event, identify relative strengths and weaknesses of each.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Convention tradeoffs</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Partial: NEEDED: Audit cost connection to convention choice (Module 3 §3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Given two conventions on the same event, identify relative strengths and weaknesses of each.</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Convention tradeoffs</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Identify predictions in balance sheet items, explain why they generate uncertainty and audit costs, including manager-auditor asymmetry.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Predictions and audit costs</t>
         </is>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -1065,150 +1033,140 @@
           <t>R</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>Partial: NEEDED: Audit cost connection to convention choice (Module 3 §3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>Not supported: NEEDED: Predictions in definitions (M4 §1) + manager-auditor asymmetry (M3 §3 or M4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Identify predictions in balance sheet items, explain why they generate uncertainty and audit costs, including manager-auditor asymmetry.</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Predictions and audit costs</t>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Given cash outflows, classify each as creating an asset or an expense, and explain what determines the difference.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Asset vs. expense</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
       <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="13" t="inlineStr">
-        <is>
-          <t>Not supported: NEEDED: Predictions in definitions (M4 §1) + manager-auditor asymmetry (M3 §3 or M4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>8 (new)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Given cash outflows, classify each as creating an asset or an expense, and explain what determines the difference.</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Asset vs. expense</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="13" t="inlineStr">
+      <c r="Q11" s="11" t="inlineStr">
         <is>
           <t>Not supported: NEEDED: Classification exercise (M4 §1 after definitions or M3-M4 bridge)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>IV. The Identity and the Architecture</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="17" t="n"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="3" t="n">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Recognize the identity is a constraint imposed on the system, and explain what it makes possible — self-balancing and error detection.</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Identity is imposed</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Module 4 §1 opens with this</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Recognize the identity is a constraint imposed on the system, and explain what it makes possible — self-balancing and error detection.</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Identity is imposed</t>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Explain that total equities is determined by A and L, and that its decomposition into components is a deliberate information design choice.</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Equities decomposition</t>
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
@@ -1217,43 +1175,43 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="O14" s="8" t="n"/>
       <c r="P14" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Module 4 §1 opens with this</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="3" t="n">
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Partial: NEEDED: Decomposition as info design (M4 §1) + restricted/unrestricted (M4 §1 nonprofit passage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Explain that total equities is determined by A and L, and that its decomposition into components is a deliberate information design choice.</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Equities decomposition</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Explain why the architecture applies to any entity, and how the decomposition of the residual changes for different entity types.</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Works for any entity</t>
         </is>
       </c>
       <c r="D15" s="8" t="n"/>
@@ -1263,42 +1221,38 @@
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>Partial: NEEDED: Decomposition as info design (M4 §1) + restricted/unrestricted (M4 §1 nonprofit passage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="3" t="n">
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Partial: NEEDED: Restricted vs. unrestricted net assets (same addition as Obj 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Explain why the architecture applies to any entity, and how the decomposition of the residual changes for different entity types.</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Works for any entity</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Given a transaction, determine affected accounts, direction of change, and verify the identity holds.</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Trace a transaction</t>
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
@@ -1308,102 +1262,110 @@
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="O16" s="8" t="n"/>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="Q16" s="12" t="inlineStr">
-        <is>
-          <t>Partial: NEEDED: Restricted vs. unrestricted net assets (same addition as Obj 10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="3" t="n">
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Transaction sequencer provides practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>V. Two Snapshots and Three Decompositions</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Given a transaction, determine affected accounts, direction of change, and verify the identity holds.</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Trace a transaction</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="10" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Explain why decomposing the change between two balance sheets adds information the change alone does not provide.</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Decomposition adds information</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="8" t="n"/>
-      <c r="Q17" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Transaction sequencer provides practice</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>V. Two Snapshots and Three Decompositions</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="17" t="n"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="3" t="n">
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Module 4 §3 + positive reframing fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Explain why decomposing the change between two balance sheets adds information the change alone does not provide.</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Decomposition adds information</t>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Identify which change each flow statement decomposes, explain what each adds, and explain the nesting of IS within SCE.</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>What each decomposes + nesting</t>
         </is>
       </c>
       <c r="D19" s="8" t="n"/>
@@ -1412,14 +1374,10 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -1429,30 +1387,34 @@
           <t>R</t>
         </is>
       </c>
-      <c r="O19" s="10" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P19" s="8" t="n"/>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>Supported: Module 4 §3 + positive reframing fits</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="3" t="n">
+          <t>Supported: Module 4 §3 covers all three; nesting is implicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Identify which change each flow statement decomposes, explain what each adds, and explain the nesting of IS within SCE.</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>What each decomposes + nesting</t>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Explain what makes cash different (convention-free + theft target) and what comparing CFO to NI reveals.</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Why single out cash</t>
         </is>
       </c>
       <c r="D20" s="8" t="n"/>
@@ -1464,7 +1426,7 @@
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -1474,102 +1436,94 @@
           <t>R</t>
         </is>
       </c>
-      <c r="O20" s="10" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Module 4 §3 covers all three; nesting is implicit</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="3" t="n">
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>Partial: Convention-free leg supported. NEEDED: Cash as theft target / safeguarding (M3 §3 or M4 §3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>VI. Reading the Statements Together</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Explain what makes cash different (convention-free + theft target) and what comparing CFO to NI reveals.</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Why single out cash</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Given transactions, trace the specific sources of the NI vs. CFO gap and explain why each produces a difference.</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>NI vs. CFO: trace it</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>Partial: Convention-free leg supported. NEEDED: Cash as theft target / safeguarding (M3 §3 or M4 §3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>VI. Reading the Statements Together</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="17" t="n"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="3" t="n">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Sequencer + Reflect 4 prompts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Given transactions, trace the specific sources of the NI vs. CFO gap and explain why each produces a difference.</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>NI vs. CFO: trace it</t>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Given a gap, interpret what it reveals and identify the questions a persistent pattern should prompt.</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>NI vs. CFO: interpret it</t>
         </is>
       </c>
       <c r="D23" s="8" t="n"/>
@@ -1582,53 +1536,61 @@
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Sequencer + Reflect 4 prompts</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="n">
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>Partial: Single-period supported. NEEDED: Brief treatment of multi-period persistence</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Given a gap, interpret what it reveals and identify the questions a persistent pattern should prompt.</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>NI vs. CFO: interpret it</t>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Recognize that some items are more convention-shaped than others; cash is the benchmark.</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Convention spectrum</t>
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="O24" s="10" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1636,33 +1598,29 @@
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="12" t="inlineStr">
         <is>
-          <t>Partial: Single-period supported. NEEDED: Brief treatment of multi-period persistence</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="3" t="n">
+          <t>Marginal: Student has pieces; hasn’t assembled them this way. Probably assessable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Recognize that some items are more convention-shaped than others; cash is the benchmark.</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Convention spectrum</t>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Starting from the change in RE, show what each successive decomposition adds — IS, then CFS comparison.</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Read statements together</t>
         </is>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="H25" s="8" t="n"/>
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
@@ -1677,129 +1635,84 @@
           <t>R</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="12" t="inlineStr">
-        <is>
-          <t>Marginal: Student has pieces; hasn't assembled them this way. Probably assessable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Starting from the change in RE, show what each successive decomposition adds — IS, then CFS comparison.</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Read statements together</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>Supported: Sequencer produces all needed data</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Primary — objective is explicitly taught here</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Reinforced — objective is revisited or built upon</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="9" t="inlineStr">
-        <is>
-          <t>Supported: Sequencer produces all needed data</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Legend:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Primary — objective is explicitly taught here</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Reinforced — objective is revisited or built upon</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Assessed — student response or exercise tests this objective</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Content Support:</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Content Support:</t>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Supported — current content develops the knowledge needed</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Supported — current content develops the knowledge needed</t>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Partial / Marginal — concept present but new content needed for full support</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Partial / Marginal — concept present but new content needed for full support</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Not supported — new content required before objective is assessable</t>
         </is>
@@ -1807,12 +1720,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A22:Q22"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="A17:Q17"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="A12:Q12"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="A5:Q5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
